--- a/ShareMarket-2025.xlsx
+++ b/ShareMarket-2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{43225DF6-7BEF-4BDB-9F84-8FD955793706}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{0FA1F1E3-9754-430C-80B6-13A2687C9C41}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8952" activeTab="4" xr2:uid="{ED50D364-8611-4D83-A6B8-5F797ED4AD3A}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="122">
   <si>
     <t>S.NO</t>
   </si>
@@ -152,9 +152,6 @@
   </si>
   <si>
     <t>23/05/2025</t>
-  </si>
-  <si>
-    <t>Intraday Stock Profit &amp; Loss Statment</t>
   </si>
   <si>
     <t>ITC</t>
@@ -412,6 +409,86 @@
   <si>
     <t>25/9/2025</t>
   </si>
+  <si>
+    <t>Intraday Stock Profit &amp; Loss Report</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Adobe Garamond Pro Bold"/>
+        <family val="1"/>
+      </rPr>
+      <t>Stock Market Daily Profit / Loss</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color rgb="FF006100"/>
+        <rFont val="Adobe Garamond Pro Bold"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>&amp;</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color rgb="FF006100"/>
+        <rFont val="Adobe Garamond Pro Bold"/>
+        <family val="1"/>
+      </rPr>
+      <t>Gold Bees ETF</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Adobe Fan Heiti Std B"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>578</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="Adobe Fan Heiti Std B"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Adobe Fan Heiti Std B"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>-55</t>
+    </r>
+  </si>
+  <si>
+    <t>0/507</t>
+  </si>
 </sst>
 </file>
 
@@ -421,7 +498,7 @@
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="61" x14ac:knownFonts="1">
+  <fonts count="65" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -491,14 +568,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FFFF0000"/>
-      <name val="Adobe Fangsong Std R"/>
-      <family val="1"/>
-      <charset val="128"/>
     </font>
     <font>
       <sz val="16"/>
@@ -862,6 +931,41 @@
       <color rgb="FF006100"/>
       <name val="Adobe Garamond Pro Bold"/>
       <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF006100"/>
+      <name val="Adobe Garamond Pro"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FFFF0000"/>
+      <name val="Adobe Garamond Pro Bold"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF006100"/>
+      <name val="Adobe Garamond Pro Bold"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF0070C0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF00B050"/>
+      <name val="Adobe Fan Heiti Std B"/>
+      <family val="2"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="5">
@@ -902,7 +1006,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="2" applyFont="1"/>
@@ -911,167 +1015,170 @@
     <xf numFmtId="10" fontId="8" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="8" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="16" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="2" fontId="16" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="10" fontId="21" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="21" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="25" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="19" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="15" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="2" fontId="15" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="10" fontId="20" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="20" fillId="4" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="24" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="18" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="19" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="19" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="25" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="18" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="24" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="19" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="18" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="32" fillId="2" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="32" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="33" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="33" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="34" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="34" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="34" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="33" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="36" fillId="2" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="38" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="38" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="40" fillId="2" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="42" fillId="2" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="42" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="37" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="37" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="36" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="44" fillId="2" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="44" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="35" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="43" fillId="2" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="43" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="35" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="36" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="36" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="35" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="33" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="32" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="42" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="42" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="18" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="2" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="48" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="41" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="41" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="2" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="47" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="48" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="47" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="48" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="42" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="50" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="51" fillId="2" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="51" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="47" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="41" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="49" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="50" fillId="2" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="50" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="51" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="50" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="2" fontId="50" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="49" fillId="2" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="2" fontId="51" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="50" fillId="2" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="52" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="53" fillId="2" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="53" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="2" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="52" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="53" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="52" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="2" fontId="52" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="53" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="54" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="4" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="55" fillId="4" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="0" fontId="56" fillId="2" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="54" fillId="4" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="52" fillId="2" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="56" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="2" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="55" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="22" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="60" fillId="2" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="62" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="59" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="64" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="14" fontId="23" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1419,10 +1526,10 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>3</v>
@@ -1437,7 +1544,7 @@
         <v>9</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="2:11" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -1455,7 +1562,7 @@
         <v>7</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G3" s="17">
         <v>287.7</v>
@@ -1484,16 +1591,16 @@
         <v>2</v>
       </c>
       <c r="C5" s="41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D5" s="41">
         <v>70</v>
       </c>
       <c r="E5" s="70" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F5" s="41" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G5" s="41">
         <v>432.95</v>
@@ -1520,16 +1627,16 @@
         <v>3</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D7" s="17">
         <v>15</v>
       </c>
       <c r="E7" s="69" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G7" s="17">
         <v>550.04999999999995</v>
@@ -1555,7 +1662,7 @@
         <v>4</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D9" s="17">
         <v>50</v>
@@ -1597,10 +1704,10 @@
         <v>40</v>
       </c>
       <c r="E11" s="69" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G11" s="28">
         <v>229.1</v>
@@ -1635,10 +1742,10 @@
         <v>50</v>
       </c>
       <c r="E13" s="69" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G13" s="17">
         <v>196.85</v>
@@ -1670,10 +1777,10 @@
         <v>12</v>
       </c>
       <c r="E15" s="69" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F15" s="69" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G15" s="28">
         <v>720.3</v>
@@ -1703,16 +1810,16 @@
         <v>8</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D17" s="17">
         <v>15</v>
       </c>
       <c r="E17" s="69" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F17" s="69" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G17" s="17">
         <v>811.45</v>
@@ -1741,7 +1848,7 @@
         <v>9</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D19" s="17">
         <v>15</v>
@@ -1766,7 +1873,7 @@
         <v>3.6365903847352956</v>
       </c>
       <c r="K19" s="30" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="2:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.4">
@@ -1804,7 +1911,7 @@
         <v>2.7056414601426209</v>
       </c>
       <c r="K21" s="30" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="2:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.4">
@@ -1817,7 +1924,7 @@
         <v>11</v>
       </c>
       <c r="C23" s="41" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D23" s="41">
         <v>40</v>
@@ -1826,7 +1933,7 @@
         <v>45814</v>
       </c>
       <c r="F23" s="70" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G23" s="41">
         <v>543.77</v>
@@ -1854,7 +1961,7 @@
         <v>12</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D25" s="17">
         <v>40</v>
@@ -1863,7 +1970,7 @@
         <v>45906</v>
       </c>
       <c r="F25" s="69" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G25" s="17">
         <v>298.67</v>
@@ -1898,7 +2005,7 @@
         <v>45906</v>
       </c>
       <c r="F27" s="70" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G27" s="41">
         <v>104.02</v>
@@ -1934,7 +2041,7 @@
         <v>45936</v>
       </c>
       <c r="F29" s="44" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G29" s="41">
         <v>255.25</v>
@@ -1962,16 +2069,16 @@
         <v>15</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D31" s="17">
         <v>18</v>
       </c>
       <c r="E31" s="35" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F31" s="71" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G31" s="17">
         <v>817.85</v>
@@ -2003,10 +2110,10 @@
         <v>22</v>
       </c>
       <c r="E33" s="44" t="s">
+        <v>70</v>
+      </c>
+      <c r="F33" s="70" t="s">
         <v>71</v>
-      </c>
-      <c r="F33" s="70" t="s">
-        <v>72</v>
       </c>
       <c r="G33" s="43">
         <v>678.45</v>
@@ -2034,16 +2141,16 @@
         <v>17</v>
       </c>
       <c r="C35" s="39" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D35" s="39">
         <v>17</v>
       </c>
       <c r="E35" s="67" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F35" s="72" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G35" s="40">
         <v>1586.9</v>
@@ -2072,16 +2179,16 @@
         <v>18</v>
       </c>
       <c r="C37" s="49" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D37" s="39">
         <v>10</v>
       </c>
       <c r="E37" s="67" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F37" s="72" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G37" s="40">
         <v>2787.5</v>
@@ -2117,10 +2224,10 @@
         <v>60</v>
       </c>
       <c r="E39" s="68" t="s">
+        <v>78</v>
+      </c>
+      <c r="F39" s="68" t="s">
         <v>79</v>
-      </c>
-      <c r="F39" s="68" t="s">
-        <v>80</v>
       </c>
       <c r="G39" s="56">
         <v>258.06</v>
@@ -2154,7 +2261,7 @@
         <v>100</v>
       </c>
       <c r="E41" s="68" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F41" s="73">
         <v>45664</v>
@@ -2230,7 +2337,7 @@
         <v>22</v>
       </c>
       <c r="C45" s="57" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D45" s="56">
         <v>50</v>
@@ -2343,7 +2450,7 @@
         <v>25</v>
       </c>
       <c r="C51" s="85" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D51" s="84">
         <v>20</v>
@@ -2378,7 +2485,7 @@
         <v>26</v>
       </c>
       <c r="C53" s="57" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D53" s="56">
         <v>100</v>
@@ -2387,7 +2494,7 @@
         <v>45907</v>
       </c>
       <c r="F53" s="86" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G53" s="81">
         <v>266.44</v>
@@ -2412,7 +2519,7 @@
         <v>27</v>
       </c>
       <c r="C55" s="57" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D55" s="56">
         <v>25</v>
@@ -2421,7 +2528,7 @@
         <v>45968</v>
       </c>
       <c r="F55" s="75" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G55" s="81">
         <v>2774.54</v>
@@ -2447,16 +2554,16 @@
         <v>28</v>
       </c>
       <c r="C57" s="91" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D57" s="90">
         <v>100</v>
       </c>
       <c r="E57" s="92" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F57" s="92" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G57" s="93">
         <v>321.85000000000002</v>
@@ -2481,16 +2588,16 @@
         <v>29</v>
       </c>
       <c r="C59" s="57" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D59" s="56">
         <v>30</v>
       </c>
       <c r="E59" s="75" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F59" s="75" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G59" s="81">
         <v>978.8</v>
@@ -2521,10 +2628,10 @@
         <v>100</v>
       </c>
       <c r="E61" s="75" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F61" s="75" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G61" s="81">
         <v>97.82</v>
@@ -2555,10 +2662,10 @@
         <v>100</v>
       </c>
       <c r="E63" s="75" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F63" s="75" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G63" s="81">
         <v>259.14999999999998</v>
@@ -2583,16 +2690,16 @@
         <v>32</v>
       </c>
       <c r="C65" s="57" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D65" s="56">
         <v>90</v>
       </c>
       <c r="E65" s="75" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F65" s="75" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G65" s="81">
         <v>854.17</v>
@@ -2617,16 +2724,16 @@
         <v>33</v>
       </c>
       <c r="C67" s="57" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D67" s="56">
         <v>25</v>
       </c>
       <c r="E67" s="75" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F67" s="75" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G67" s="81">
         <v>957.45</v>
@@ -2657,7 +2764,7 @@
         <v>100</v>
       </c>
       <c r="E69" s="78" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F69" s="78"/>
       <c r="G69" s="80">
@@ -2674,7 +2781,7 @@
         <v>35</v>
       </c>
       <c r="C71" s="57" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D71" s="56">
         <v>100</v>
@@ -2683,7 +2790,7 @@
         <v>45755</v>
       </c>
       <c r="F71" s="75" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G71" s="81">
         <v>286.39999999999998</v>
@@ -2699,7 +2806,7 @@
         <v>0.66340782122906228</v>
       </c>
       <c r="K71" s="96" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="72" spans="1:11" ht="25.8" x14ac:dyDescent="0.5">
@@ -2711,7 +2818,7 @@
         <v>36</v>
       </c>
       <c r="C73" s="57" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D73" s="56">
         <v>30</v>
@@ -2786,13 +2893,13 @@
         <v>38</v>
       </c>
       <c r="C77" s="91" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D77" s="90">
         <v>51</v>
       </c>
       <c r="E77" s="92" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F77" s="92">
         <v>45938</v>
@@ -2819,16 +2926,16 @@
         <v>39</v>
       </c>
       <c r="C79" s="57" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D79" s="56">
         <v>250</v>
       </c>
       <c r="E79" s="75" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F79" s="75" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G79" s="81">
         <v>92.91</v>
@@ -2859,10 +2966,10 @@
         <v>250</v>
       </c>
       <c r="E81" s="75" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F81" s="75" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G81" s="81">
         <v>93.41</v>
@@ -2888,13 +2995,13 @@
         <v>41</v>
       </c>
       <c r="C83" s="77" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D83" s="76">
         <v>25</v>
       </c>
       <c r="E83" s="78" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F83" s="78"/>
       <c r="G83" s="80">
@@ -2914,13 +3021,13 @@
         <v>42</v>
       </c>
       <c r="C85" s="57" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D85" s="56">
         <v>55</v>
       </c>
       <c r="E85" s="75" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F85" s="75">
         <v>45788</v>
@@ -2947,13 +3054,13 @@
         <v>43</v>
       </c>
       <c r="C87" s="57" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D87" s="56">
         <v>100</v>
       </c>
       <c r="E87" s="75" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F87" s="75">
         <v>45698</v>
@@ -2979,13 +3086,13 @@
         <v>44</v>
       </c>
       <c r="C89" s="77" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D89" s="76">
         <v>30</v>
       </c>
       <c r="E89" s="78" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F89" s="78"/>
       <c r="G89" s="80">
@@ -3006,7 +3113,7 @@
         <v>100</v>
       </c>
       <c r="E91" s="78" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F91" s="78"/>
       <c r="G91" s="80">
@@ -3050,10 +3157,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -3068,7 +3175,7 @@
         <v>9</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="1.35">
@@ -3088,13 +3195,13 @@
     <row r="3" spans="1:15" ht="14.4" customHeight="1" x14ac:dyDescent="1.35">
       <c r="A3" s="24"/>
       <c r="B3" s="24" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C3" s="24">
         <v>35</v>
       </c>
       <c r="D3" s="24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E3" s="24" t="s">
         <v>8</v>
@@ -3143,13 +3250,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C5" s="24">
         <v>20</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E5" s="24" t="s">
         <v>8</v>
@@ -3179,13 +3286,13 @@
         <v>2</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C7" s="24">
         <v>50</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E7" s="24" t="s">
         <v>8</v>
@@ -3224,13 +3331,13 @@
         <v>3</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C9" s="24">
         <v>250</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E9" s="24"/>
       <c r="F9" s="25">
@@ -3267,13 +3374,13 @@
         <v>4</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C11" s="24">
         <v>25</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E11" s="24" t="s">
         <v>8</v>
@@ -3318,7 +3425,7 @@
         <v>10</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E13" s="24" t="s">
         <v>8</v>
@@ -3348,13 +3455,13 @@
         <v>6</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C15" s="24">
         <v>50</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E15" s="24" t="s">
         <v>8</v>
@@ -3399,10 +3506,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="38" t="s">
         <v>75</v>
-      </c>
-      <c r="C1" s="38" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="18.600000000000001" x14ac:dyDescent="0.4">
@@ -3410,7 +3517,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="36" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C2" s="37">
         <v>-902</v>
@@ -3421,7 +3528,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -3454,7 +3561,7 @@
         <v>13</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>14</v>
@@ -3720,13 +3827,13 @@
       <c r="E17" s="6">
         <v>229.02</v>
       </c>
-      <c r="L17" s="103" t="s">
+      <c r="L17" s="108" t="s">
         <v>10</v>
       </c>
-      <c r="M17" s="103"/>
-      <c r="N17" s="103"/>
-      <c r="O17" s="103"/>
-      <c r="P17" s="103"/>
+      <c r="M17" s="108"/>
+      <c r="N17" s="108"/>
+      <c r="O17" s="108"/>
+      <c r="P17" s="108"/>
     </row>
     <row r="18" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
@@ -3744,11 +3851,11 @@
       <c r="E18" s="6">
         <v>101.04</v>
       </c>
-      <c r="L18" s="103"/>
-      <c r="M18" s="103"/>
-      <c r="N18" s="103"/>
-      <c r="O18" s="103"/>
-      <c r="P18" s="103"/>
+      <c r="L18" s="108"/>
+      <c r="M18" s="108"/>
+      <c r="N18" s="108"/>
+      <c r="O18" s="108"/>
+      <c r="P18" s="108"/>
     </row>
     <row r="19" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
@@ -3871,7 +3978,7 @@
     </row>
     <row r="27" spans="1:16" ht="18" x14ac:dyDescent="0.35">
       <c r="C27" s="16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
@@ -3882,7 +3989,7 @@
         <v>12</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D28" s="5">
         <v>2.46E-2</v>
@@ -3899,7 +4006,7 @@
         <v>16</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D29" s="5">
         <v>3.5000000000000001E-3</v>
@@ -3916,7 +4023,7 @@
         <v>15</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D30" s="5">
         <v>1.1000000000000001E-3</v>
@@ -3933,7 +4040,7 @@
         <v>17</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D31" s="5">
         <v>2.0000000000000001E-4</v>
@@ -3950,7 +4057,7 @@
         <v>18</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D32" s="12">
         <v>-2.3999999999999998E-3</v>
@@ -3967,7 +4074,7 @@
         <v>19</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D33" s="5">
         <v>-7.1000000000000004E-3</v>
@@ -3984,7 +4091,7 @@
         <v>20</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D34" s="5">
         <v>6.4000000000000003E-3</v>
@@ -4001,7 +4108,7 @@
         <v>21</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D35" s="5">
         <v>5.7000000000000002E-3</v>
@@ -4018,7 +4125,7 @@
         <v>22</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D36" s="12">
         <v>-1.54E-2</v>
@@ -4036,7 +4143,7 @@
         <v>23</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D37" s="12">
         <v>-2.69E-2</v>
@@ -4053,7 +4160,7 @@
         <v>24</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D38" s="5">
         <v>4.7000000000000002E-3</v>
@@ -4070,7 +4177,7 @@
         <v>25</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D39" s="5">
         <v>8.0000000000000002E-3</v>
@@ -4087,7 +4194,7 @@
         <v>26</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D40" s="5">
         <v>9.4000000000000004E-3</v>
@@ -4104,7 +4211,7 @@
         <v>27</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D41" s="5">
         <v>1.8700000000000001E-2</v>
@@ -4121,7 +4228,7 @@
         <v>28</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D42" s="5">
         <v>3.7199999999999997E-2</v>
@@ -4138,7 +4245,7 @@
         <v>29</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D43" s="12">
         <v>-6.7000000000000002E-3</v>
@@ -4155,7 +4262,7 @@
         <v>30</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D44" s="5">
         <v>1E-3</v>
@@ -4172,7 +4279,7 @@
         <v>31</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D45" s="12">
         <v>-1.1000000000000001E-3</v>
@@ -4189,7 +4296,7 @@
         <v>32</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D46" s="12">
         <v>-8.9999999999999998E-4</v>
@@ -4206,7 +4313,7 @@
         <v>33</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D47" s="12">
         <v>-2.47E-2</v>
@@ -4223,7 +4330,7 @@
         <v>34</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D48" s="5">
         <v>1E-3</v>
@@ -4240,7 +4347,7 @@
         <v>35</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D49" s="12">
         <v>-8.9999999999999998E-4</v>
@@ -4257,7 +4364,7 @@
         <v>37</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D50" s="5">
         <v>2.6200000000000001E-2</v>
@@ -4268,7 +4375,7 @@
     </row>
     <row r="52" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="C52" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
@@ -4276,10 +4383,10 @@
         <v>1</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D54" s="12">
         <v>-2.0299999999999999E-2</v>
@@ -4296,7 +4403,7 @@
         <v>12</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D55" s="12">
         <v>-7.1999999999999998E-3</v>
@@ -4313,7 +4420,7 @@
         <v>16</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D56" s="5">
         <v>8.8000000000000005E-3</v>
@@ -4330,7 +4437,7 @@
         <v>15</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D57" s="12">
         <v>-1.72E-2</v>
@@ -4347,7 +4454,7 @@
         <v>17</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D58" s="12">
         <v>-1.0999999999999999E-2</v>
@@ -4356,7 +4463,7 @@
         <v>148.33000000000001</v>
       </c>
       <c r="G58" s="22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
@@ -4367,7 +4474,7 @@
         <v>18</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D59" s="12">
         <v>-3.3E-3</v>
@@ -4384,7 +4491,7 @@
         <v>19</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D60" s="5">
         <v>8.0999999999999996E-3</v>
@@ -4393,7 +4500,7 @@
         <v>335.05</v>
       </c>
       <c r="G60" s="23" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
@@ -4404,7 +4511,7 @@
         <v>20</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D61" s="12">
         <v>-6.4999999999999997E-3</v>
@@ -4421,7 +4528,7 @@
         <v>21</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D62" s="5">
         <v>5.7000000000000002E-3</v>
@@ -4438,7 +4545,7 @@
         <v>22</v>
       </c>
       <c r="C63" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D63" s="19">
         <v>8.2000000000000007E-3</v>
@@ -4455,7 +4562,7 @@
         <v>23</v>
       </c>
       <c r="C64" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D64" s="19">
         <v>2.0999999999999999E-3</v>
@@ -4472,7 +4579,7 @@
         <v>24</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D65" s="5">
         <v>6.1999999999999998E-3</v>
@@ -4489,7 +4596,7 @@
         <v>25</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D66" s="12">
         <v>-1.14E-2</v>
@@ -4506,7 +4613,7 @@
         <v>26</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D67" s="12">
         <v>-1.44E-2</v>
@@ -4523,7 +4630,7 @@
         <v>27</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D68" s="12">
         <v>-1.84E-2</v>
@@ -4540,7 +4647,7 @@
         <v>28</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D69" s="12">
         <v>-8.8000000000000005E-3</v>
@@ -4557,7 +4664,7 @@
         <v>29</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D70" s="5">
         <v>7.4000000000000003E-3</v>
@@ -4575,7 +4682,7 @@
         <v>30</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D71" s="5">
         <v>2.5399999999999999E-2</v>
@@ -4593,7 +4700,7 @@
         <v>31</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D72" s="12">
         <v>-4.4999999999999997E-3</v>
@@ -4610,7 +4717,7 @@
         <v>32</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D73" s="5">
         <v>8.8000000000000005E-3</v>
@@ -4628,7 +4735,7 @@
         <v>33</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D74" s="12">
         <v>-1.01E-2</v>
@@ -4645,7 +4752,7 @@
         <v>34</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D75" s="5">
         <v>2.2000000000000001E-3</v>
@@ -4662,7 +4769,7 @@
         <v>35</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D76" s="12">
         <v>-9.7999999999999997E-3</v>
@@ -4679,7 +4786,7 @@
         <v>37</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D77" s="5">
         <v>3.4200000000000001E-2</v>
@@ -4704,49 +4811,52 @@
   <cols>
     <col min="7" max="7" width="20.33203125" customWidth="1"/>
     <col min="8" max="8" width="26.77734375" customWidth="1"/>
-    <col min="9" max="9" width="19.33203125" customWidth="1"/>
-    <col min="10" max="10" width="25.109375" customWidth="1"/>
+    <col min="9" max="9" width="25.77734375" customWidth="1"/>
+    <col min="10" max="10" width="53.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="G2" s="104" t="s">
-        <v>41</v>
-      </c>
-      <c r="H2" s="105"/>
-      <c r="I2" s="105"/>
+    <row r="2" spans="5:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="109"/>
+      <c r="H2" s="109"/>
+      <c r="I2" s="109"/>
     </row>
     <row r="3" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="G3" s="105"/>
-      <c r="H3" s="105"/>
-      <c r="I3" s="105"/>
+      <c r="G3" s="109"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="109"/>
     </row>
     <row r="4" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="G4" s="105"/>
-      <c r="H4" s="105"/>
-      <c r="I4" s="105"/>
+      <c r="G4" s="109"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
     </row>
     <row r="5" spans="5:10" ht="36.6" x14ac:dyDescent="0.7">
       <c r="E5" s="102"/>
-      <c r="I5" s="106" t="s">
-        <v>54</v>
-      </c>
-      <c r="J5" s="106"/>
+      <c r="F5" s="107" t="s">
+        <v>118</v>
+      </c>
+      <c r="G5" s="107"/>
+      <c r="H5" s="106"/>
+      <c r="I5" s="110" t="s">
+        <v>119</v>
+      </c>
+      <c r="J5" s="111"/>
     </row>
     <row r="6" spans="5:10" ht="21.6" x14ac:dyDescent="0.45">
       <c r="F6" s="10" t="s">
         <v>36</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H6" s="10" t="s">
         <v>39</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="5:10" ht="18.600000000000001" x14ac:dyDescent="0.4">
@@ -4759,10 +4869,10 @@
       <c r="H8" s="97">
         <v>8</v>
       </c>
-      <c r="I8" s="107" t="s">
-        <v>118</v>
-      </c>
-      <c r="J8" s="108">
+      <c r="I8" s="103" t="s">
+        <v>117</v>
+      </c>
+      <c r="J8" s="112">
         <v>80</v>
       </c>
     </row>
@@ -4771,15 +4881,15 @@
         <v>2</v>
       </c>
       <c r="G9" s="97" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H9" s="97">
         <v>19</v>
       </c>
-      <c r="I9" s="107" t="s">
-        <v>110</v>
-      </c>
-      <c r="J9" s="108">
+      <c r="I9" s="103" t="s">
+        <v>109</v>
+      </c>
+      <c r="J9" s="112">
         <v>80</v>
       </c>
     </row>
@@ -4788,15 +4898,15 @@
         <v>3</v>
       </c>
       <c r="G10" s="97" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H10" s="97">
         <v>42</v>
       </c>
-      <c r="I10" s="107" t="s">
-        <v>118</v>
-      </c>
-      <c r="J10" s="108">
+      <c r="I10" s="103" t="s">
+        <v>117</v>
+      </c>
+      <c r="J10" s="112">
         <v>120</v>
       </c>
     </row>
@@ -4805,15 +4915,15 @@
         <v>4</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H11" s="9">
         <v>-850</v>
       </c>
-      <c r="I11" s="107" t="s">
-        <v>117</v>
-      </c>
-      <c r="J11" s="108">
+      <c r="I11" s="103" t="s">
+        <v>116</v>
+      </c>
+      <c r="J11" s="112">
         <v>100</v>
       </c>
     </row>
@@ -4823,15 +4933,15 @@
         <v>5</v>
       </c>
       <c r="G12" s="97" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H12" s="97">
         <v>60</v>
       </c>
-      <c r="I12" s="107" t="s">
-        <v>116</v>
-      </c>
-      <c r="J12" s="108">
+      <c r="I12" s="103" t="s">
+        <v>115</v>
+      </c>
+      <c r="J12" s="112">
         <v>120</v>
       </c>
     </row>
@@ -4840,15 +4950,15 @@
         <v>6</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H13" s="9">
         <v>-1000</v>
       </c>
-      <c r="I13" s="107" t="s">
-        <v>115</v>
-      </c>
-      <c r="J13" s="108">
+      <c r="I13" s="103" t="s">
+        <v>114</v>
+      </c>
+      <c r="J13" s="112">
         <v>100</v>
       </c>
     </row>
@@ -4857,15 +4967,15 @@
         <v>7</v>
       </c>
       <c r="G14" s="97" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H14" s="97">
         <v>220</v>
       </c>
-      <c r="I14" s="109">
+      <c r="I14" s="105">
         <v>45667</v>
       </c>
-      <c r="J14" s="108">
+      <c r="J14" s="112">
         <v>70</v>
       </c>
     </row>
@@ -4874,15 +4984,15 @@
         <v>8</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H15" s="9">
         <v>-1150</v>
       </c>
-      <c r="I15" s="109">
+      <c r="I15" s="105">
         <v>45726</v>
       </c>
-      <c r="J15" s="108">
+      <c r="J15" s="112">
         <v>60</v>
       </c>
     </row>
@@ -4896,10 +5006,10 @@
       <c r="H16" s="97">
         <v>78</v>
       </c>
-      <c r="I16" s="109">
+      <c r="I16" s="105">
         <v>45818</v>
       </c>
-      <c r="J16" s="108">
+      <c r="J16" s="112">
         <v>90</v>
       </c>
     </row>
@@ -4913,10 +5023,10 @@
       <c r="H17" s="97">
         <v>245</v>
       </c>
-      <c r="I17" s="109">
+      <c r="I17" s="105">
         <v>45848</v>
       </c>
-      <c r="J17" s="108">
+      <c r="J17" s="112">
         <v>100</v>
       </c>
     </row>
@@ -4930,18 +5040,29 @@
       <c r="H18" s="97">
         <v>565</v>
       </c>
-      <c r="I18" s="109">
+      <c r="I18" s="105">
         <v>45879</v>
       </c>
-      <c r="J18" s="108">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="19" spans="6:10" ht="21.6" x14ac:dyDescent="0.45">
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
+      <c r="J18" s="112" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="19" spans="6:10" ht="18.600000000000001" x14ac:dyDescent="0.4">
+      <c r="F19" s="97">
+        <v>12</v>
+      </c>
+      <c r="G19" s="101">
+        <v>45910</v>
+      </c>
+      <c r="H19" s="97">
+        <v>490</v>
+      </c>
+      <c r="I19" s="105">
+        <v>45910</v>
+      </c>
+      <c r="J19" s="104" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="20" spans="6:10" ht="21.6" x14ac:dyDescent="0.45">
       <c r="F20" s="8"/>

--- a/ShareMarket-2025.xlsx
+++ b/ShareMarket-2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{0FA1F1E3-9754-430C-80B6-13A2687C9C41}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{6C03CD62-EEDF-4F5A-983D-4D769AEB63BC}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8952" activeTab="4" xr2:uid="{ED50D364-8611-4D83-A6B8-5F797ED4AD3A}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="123">
   <si>
     <t>S.NO</t>
   </si>
@@ -488,6 +488,38 @@
   </si>
   <si>
     <t>0/507</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Adobe Fan Heiti Std B"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>622</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="Adobe Fan Heiti Std B"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Adobe Fan Heiti Std B"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>-400</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1167,6 +1199,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="60" fillId="2" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="64" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1176,9 +1211,6 @@
     </xf>
     <xf numFmtId="0" fontId="59" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3334,14 +3366,14 @@
         <v>53</v>
       </c>
       <c r="C9" s="24">
-        <v>250</v>
-      </c>
-      <c r="D9" s="33" t="s">
-        <v>102</v>
+        <v>500</v>
+      </c>
+      <c r="D9" s="33">
+        <v>45726</v>
       </c>
       <c r="E9" s="24"/>
       <c r="F9" s="25">
-        <v>91.39</v>
+        <v>96.84</v>
       </c>
       <c r="G9" s="24">
         <v>0</v>
@@ -3354,7 +3386,7 @@
       </c>
       <c r="J9" s="27">
         <f t="shared" si="2"/>
-        <v>22847.5</v>
+        <v>48420</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="25.8" x14ac:dyDescent="0.5">
@@ -3827,13 +3859,13 @@
       <c r="E17" s="6">
         <v>229.02</v>
       </c>
-      <c r="L17" s="108" t="s">
+      <c r="L17" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="M17" s="108"/>
-      <c r="N17" s="108"/>
-      <c r="O17" s="108"/>
-      <c r="P17" s="108"/>
+      <c r="M17" s="109"/>
+      <c r="N17" s="109"/>
+      <c r="O17" s="109"/>
+      <c r="P17" s="109"/>
     </row>
     <row r="18" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
@@ -3851,11 +3883,11 @@
       <c r="E18" s="6">
         <v>101.04</v>
       </c>
-      <c r="L18" s="108"/>
-      <c r="M18" s="108"/>
-      <c r="N18" s="108"/>
-      <c r="O18" s="108"/>
-      <c r="P18" s="108"/>
+      <c r="L18" s="109"/>
+      <c r="M18" s="109"/>
+      <c r="N18" s="109"/>
+      <c r="O18" s="109"/>
+      <c r="P18" s="109"/>
     </row>
     <row r="19" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
@@ -4816,19 +4848,19 @@
   </cols>
   <sheetData>
     <row r="2" spans="5:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G2" s="109"/>
-      <c r="H2" s="109"/>
-      <c r="I2" s="109"/>
+      <c r="G2" s="110"/>
+      <c r="H2" s="110"/>
+      <c r="I2" s="110"/>
     </row>
     <row r="3" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="G3" s="109"/>
-      <c r="H3" s="109"/>
-      <c r="I3" s="109"/>
+      <c r="G3" s="110"/>
+      <c r="H3" s="110"/>
+      <c r="I3" s="110"/>
     </row>
     <row r="4" spans="5:10" x14ac:dyDescent="0.3">
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
     </row>
     <row r="5" spans="5:10" ht="36.6" x14ac:dyDescent="0.7">
       <c r="E5" s="102"/>
@@ -4837,10 +4869,10 @@
       </c>
       <c r="G5" s="107"/>
       <c r="H5" s="106"/>
-      <c r="I5" s="110" t="s">
+      <c r="I5" s="111" t="s">
         <v>119</v>
       </c>
-      <c r="J5" s="111"/>
+      <c r="J5" s="112"/>
     </row>
     <row r="6" spans="5:10" ht="21.6" x14ac:dyDescent="0.45">
       <c r="F6" s="10" t="s">
@@ -4872,7 +4904,7 @@
       <c r="I8" s="103" t="s">
         <v>117</v>
       </c>
-      <c r="J8" s="112">
+      <c r="J8" s="108">
         <v>80</v>
       </c>
     </row>
@@ -4889,7 +4921,7 @@
       <c r="I9" s="103" t="s">
         <v>109</v>
       </c>
-      <c r="J9" s="112">
+      <c r="J9" s="108">
         <v>80</v>
       </c>
     </row>
@@ -4906,7 +4938,7 @@
       <c r="I10" s="103" t="s">
         <v>117</v>
       </c>
-      <c r="J10" s="112">
+      <c r="J10" s="108">
         <v>120</v>
       </c>
     </row>
@@ -4923,7 +4955,7 @@
       <c r="I11" s="103" t="s">
         <v>116</v>
       </c>
-      <c r="J11" s="112">
+      <c r="J11" s="108">
         <v>100</v>
       </c>
     </row>
@@ -4941,7 +4973,7 @@
       <c r="I12" s="103" t="s">
         <v>115</v>
       </c>
-      <c r="J12" s="112">
+      <c r="J12" s="108">
         <v>120</v>
       </c>
     </row>
@@ -4958,7 +4990,7 @@
       <c r="I13" s="103" t="s">
         <v>114</v>
       </c>
-      <c r="J13" s="112">
+      <c r="J13" s="108">
         <v>100</v>
       </c>
     </row>
@@ -4975,7 +5007,7 @@
       <c r="I14" s="105">
         <v>45667</v>
       </c>
-      <c r="J14" s="112">
+      <c r="J14" s="108">
         <v>70</v>
       </c>
     </row>
@@ -4992,7 +5024,7 @@
       <c r="I15" s="105">
         <v>45726</v>
       </c>
-      <c r="J15" s="112">
+      <c r="J15" s="108">
         <v>60</v>
       </c>
     </row>
@@ -5009,7 +5041,7 @@
       <c r="I16" s="105">
         <v>45818</v>
       </c>
-      <c r="J16" s="112">
+      <c r="J16" s="108">
         <v>90</v>
       </c>
     </row>
@@ -5026,7 +5058,7 @@
       <c r="I17" s="105">
         <v>45848</v>
       </c>
-      <c r="J17" s="112">
+      <c r="J17" s="108">
         <v>100</v>
       </c>
     </row>
@@ -5043,7 +5075,7 @@
       <c r="I18" s="105">
         <v>45879</v>
       </c>
-      <c r="J18" s="112" t="s">
+      <c r="J18" s="108" t="s">
         <v>121</v>
       </c>
     </row>
@@ -5064,11 +5096,22 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="6:10" ht="21.6" x14ac:dyDescent="0.45">
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
+    <row r="20" spans="6:10" ht="18.600000000000001" x14ac:dyDescent="0.4">
+      <c r="F20" s="97">
+        <v>12</v>
+      </c>
+      <c r="G20" s="101">
+        <v>45940</v>
+      </c>
+      <c r="H20" s="97">
+        <v>320</v>
+      </c>
+      <c r="I20" s="105">
+        <v>45940</v>
+      </c>
+      <c r="J20" s="104" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="21" spans="6:10" ht="21.6" x14ac:dyDescent="0.45">
       <c r="F21" s="8"/>
